--- a/output/REVISION_MATCH_10.07.24.xlsx
+++ b/output/REVISION_MATCH_10.07.24.xlsx
@@ -520,7 +520,11 @@
           <t>SKU-1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Товар A</t>
+        </is>
+      </c>
       <c r="L2" t="n">
         <v>100</v>
       </c>

--- a/output/REVISION_MATCH_10.07.24.xlsx
+++ b/output/REVISION_MATCH_10.07.24.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,6 +482,11 @@
           <t>MATCH_REASONS</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Отгружено</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -529,6 +534,9 @@
         <v>100</v>
       </c>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="3">
       <c r="B3" t="n">
